--- a/inst/extdata/medication_with_codes.xlsx
+++ b/inst/extdata/medication_with_codes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sheej\Documents\Sheeja_WinLap\repos\packDAMipd\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA2EE7D-ABFB-4D6F-87AD-6B04D4750247}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088C5131-7E87-45A4-BB7C-6DDD14EC5141}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="1335" windowWidth="16905" windowHeight="9585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="medication_baseline" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>pat_TrialArm</t>
   </si>
@@ -47,24 +47,12 @@
     <t>M</t>
   </si>
   <si>
-    <t>Buprenorphine</t>
-  </si>
-  <si>
-    <t>once a week</t>
-  </si>
-  <si>
-    <t>once a day</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>Fentanyl</t>
-  </si>
-  <si>
     <t>patch_strength_1</t>
   </si>
   <si>
@@ -101,60 +89,18 @@
     <t>tab_frequency_2</t>
   </si>
   <si>
-    <t>200mcg</t>
-  </si>
-  <si>
     <t>liq_strength_1</t>
   </si>
   <si>
     <t>liq_strength_2</t>
   </si>
   <si>
-    <t>liq_frequency_2</t>
-  </si>
-  <si>
-    <t>liq_strength_3</t>
-  </si>
-  <si>
-    <t>liq_dose_unit_3</t>
-  </si>
-  <si>
     <t>liq_bottle_size_1</t>
   </si>
   <si>
-    <t>100ml</t>
-  </si>
-  <si>
     <t>liq_lasts_1</t>
   </si>
   <si>
-    <t>12 days</t>
-  </si>
-  <si>
-    <t>2days</t>
-  </si>
-  <si>
-    <t>7 days</t>
-  </si>
-  <si>
-    <t>2000ml</t>
-  </si>
-  <si>
-    <t>20mg/ml</t>
-  </si>
-  <si>
-    <t>50mg/ml</t>
-  </si>
-  <si>
-    <t>liq_lasts_2</t>
-  </si>
-  <si>
-    <t>liq_bottle_size_3</t>
-  </si>
-  <si>
-    <t>liq_lasts_3</t>
-  </si>
-  <si>
     <t>patch_name_1</t>
   </si>
   <si>
@@ -173,9 +119,6 @@
     <t>liq_name_2</t>
   </si>
   <si>
-    <t>liq_name_3</t>
-  </si>
-  <si>
     <t>patch_brand_1</t>
   </si>
   <si>
@@ -185,15 +128,6 @@
     <t>tab_brand_1</t>
   </si>
   <si>
-    <t>Temgesic</t>
-  </si>
-  <si>
-    <t>2mg</t>
-  </si>
-  <si>
-    <t>twice a day</t>
-  </si>
-  <si>
     <t>tab_brand_2</t>
   </si>
   <si>
@@ -201,6 +135,21 @@
   </si>
   <si>
     <t>patch_unit_str_2</t>
+  </si>
+  <si>
+    <t>tab_unit_1</t>
+  </si>
+  <si>
+    <t>liq_unit_1</t>
+  </si>
+  <si>
+    <t>tab_unit_2</t>
+  </si>
+  <si>
+    <t>liq_vol_1</t>
+  </si>
+  <si>
+    <t>liq_time_1</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AP3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="6.85546875" customWidth="1"/>
@@ -1055,11 +1004,17 @@
     <col min="14" max="14" width="9.28515625" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" customWidth="1"/>
     <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" customWidth="1"/>
+    <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="22" max="22" width="10.85546875" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1071,112 +1026,121 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
+        <v>35</v>
+      </c>
+      <c r="U1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="V1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" t="s">
-        <v>50</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="Z1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AB1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="AE1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF1" t="s">
         <v>21</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>25</v>
       </c>
       <c r="AG1" t="s">
         <v>38</v>
       </c>
       <c r="AH1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="AJ1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AL1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP1" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1225,82 +1189,91 @@
       <c r="P2">
         <v>3</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>2</v>
+      </c>
+      <c r="U2">
         <v>5</v>
       </c>
-      <c r="R2" t="s">
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>2</v>
+      </c>
+      <c r="Y2">
+        <v>200</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
         <v>5</v>
       </c>
-      <c r="S2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T2">
-        <v>5</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="AB2">
+        <v>3</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>20</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>100</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>12</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>2</v>
+      </c>
+      <c r="AK2">
+        <v>20</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>2000</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
         <v>7</v>
       </c>
-      <c r="V2" t="s">
-        <v>5</v>
-      </c>
-      <c r="W2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>6</v>
+      <c r="AP2">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1326,20 +1299,23 @@
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="Q3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" t="s">
-        <v>23</v>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>200</v>
       </c>
       <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
         <v>2</v>
       </c>
-      <c r="U3" t="s">
-        <v>53</v>
+      <c r="V3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
